--- a/docs/harness/wirelist/RearLights-wirelist.xlsx
+++ b/docs/harness/wirelist/RearLights-wirelist.xlsx
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AE3" s="38" t="inlineStr">
         <is>
-          <t>flying lead FL_H6_C2: EWD H6 pin A-2 W-B (factory wiring; new wire here); splice sp_rl_gnd named in SoT</t>
+          <t>flying lead FL_H6_C2: EWD H6 pin A-2 W-B (factory wiring; new wire here); splice sp_rl_gnd: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF3" s="38" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="AE4" s="54" t="inlineStr">
         <is>
-          <t>flying lead FL_OEM_JB1_1F_C1: EWD J/B1 pin 1F-1 G; splice sp_rl_tail named in SoT</t>
+          <t>flying lead FL_OEM_JB1_1F_C1: EWD J/B1 pin 1F-1 G; splice sp_rl_tail: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF4" s="54" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="AE7" s="38" t="inlineStr">
         <is>
-          <t>flying lead FL_L1_C2: EWD L1 pin 2 W-B (factory wiring; new wire here); splice sp_rl_gnd named in SoT</t>
+          <t>flying lead FL_L1_C2: EWD L1 pin 2 W-B (factory wiring; new wire here); splice sp_rl_gnd: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF7" s="38" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="AE8" s="54" t="inlineStr">
         <is>
-          <t>flying lead FL_R11_C5: EWD R11 pin 5 W-B (factory wiring; new wire here); splice sp_rl_gnd named in SoT</t>
+          <t>flying lead FL_R11_C5: EWD R11 pin 5 W-B (factory wiring; new wire here); splice sp_rl_gnd: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF8" s="54" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="AE9" s="38" t="inlineStr">
         <is>
-          <t>flying lead FL_R12_C5: EWD R12 pin 5 W-B (factory wiring; new wire here); splice sp_rl_gnd named in SoT</t>
+          <t>flying lead FL_R12_C5: EWD R12 pin 5 W-B (factory wiring; new wire here); splice sp_rl_gnd: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF9" s="38" t="inlineStr">
@@ -2091,12 +2091,12 @@
       <c r="P10" s="45" t="inlineStr"/>
       <c r="Q10" s="46" t="inlineStr">
         <is>
-          <t>opto8.i1</t>
+          <t>opto8.IN1</t>
         </is>
       </c>
       <c r="R10" s="47" t="inlineStr">
         <is>
-          <t>Brake on +12 V (opto8 i1)</t>
+          <t>Brake on +12 V (opto8 IN1)</t>
         </is>
       </c>
       <c r="S10" s="48" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="AE10" s="54" t="inlineStr">
         <is>
-          <t>flying lead FL_OEM_S9_C1: EWD S9 pin 1 G-W; splice sp_rl_stop named in SoT</t>
+          <t>flying lead FL_OEM_S9_C1: EWD S9 pin 1 G-W; splice sp_rl_stop: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF10" s="54" t="inlineStr">
@@ -2260,12 +2260,12 @@
       <c r="AD11" s="38" t="inlineStr"/>
       <c r="AE11" s="38" t="inlineStr">
         <is>
-          <t>splice sp_rl_gnd named in SoT</t>
+          <t>splice sp_rl_gnd: node of the wire list (SoT); end t_rl_gnd_bl: end row of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF11" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: end t_rl_gnd_bl (Ground point BL, back panel center (EWD 1993 p.112)) is drawing-only: not named in the SoT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG11" s="38" t="inlineStr"/>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="AE12" s="54" t="inlineStr">
         <is>
-          <t>splice sp_rl_rev named in SoT; flying lead FL_R11_C4: EWD R11 pin 4 R-B (factory wiring; new wire here)</t>
+          <t>splice sp_rl_rev: node of the wire list (SoT); flying lead FL_R11_C4: EWD R11 pin 4 R-B (factory wiring; new wire here)</t>
         </is>
       </c>
       <c r="AF12" s="54" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="AE13" s="38" t="inlineStr">
         <is>
-          <t>splice sp_rl_rev named in SoT; flying lead FL_R12_C4: EWD R12 pin 4 R-B (factory wiring; new wire here)</t>
+          <t>splice sp_rl_rev: node of the wire list (SoT); flying lead FL_R12_C4: EWD R12 pin 4 R-B (factory wiring; new wire here)</t>
         </is>
       </c>
       <c r="AF13" s="38" t="inlineStr">
@@ -2599,12 +2599,12 @@
       <c r="P14" s="45" t="inlineStr"/>
       <c r="Q14" s="46" t="inlineStr">
         <is>
-          <t>opto8.i1</t>
+          <t>opto8.IN1</t>
         </is>
       </c>
       <c r="R14" s="47" t="inlineStr">
         <is>
-          <t>Brake on +12 V (opto8 i1)</t>
+          <t>Brake on +12 V (opto8 IN1)</t>
         </is>
       </c>
       <c r="S14" s="48" t="inlineStr">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="AE14" s="54" t="inlineStr">
         <is>
-          <t>splice sp_rl_stop named in SoT; flying lead FL_H6_C1: EWD H6 pin A-1 G-W (factory wiring; new wire here)</t>
+          <t>splice sp_rl_stop: node of the wire list (SoT); flying lead FL_H6_C1: EWD H6 pin A-1 G-W (factory wiring; new wire here)</t>
         </is>
       </c>
       <c r="AF14" s="54" t="inlineStr">
@@ -2730,12 +2730,12 @@
       <c r="P15" s="29" t="inlineStr"/>
       <c r="Q15" s="30" t="inlineStr">
         <is>
-          <t>opto8.i1</t>
+          <t>opto8.IN1</t>
         </is>
       </c>
       <c r="R15" s="31" t="inlineStr">
         <is>
-          <t>Brake on +12 V (opto8 i1)</t>
+          <t>Brake on +12 V (opto8 IN1)</t>
         </is>
       </c>
       <c r="S15" s="32" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="AE15" s="38" t="inlineStr">
         <is>
-          <t>splice sp_rl_stop named in SoT; flying lead FL_R11_C1: EWD R11 pin 1 G-W (factory wiring; new wire here)</t>
+          <t>splice sp_rl_stop: node of the wire list (SoT); flying lead FL_R11_C1: EWD R11 pin 1 G-W (factory wiring; new wire here)</t>
         </is>
       </c>
       <c r="AF15" s="38" t="inlineStr">
@@ -2861,12 +2861,12 @@
       <c r="P16" s="45" t="inlineStr"/>
       <c r="Q16" s="46" t="inlineStr">
         <is>
-          <t>opto8.i1</t>
+          <t>opto8.IN1</t>
         </is>
       </c>
       <c r="R16" s="47" t="inlineStr">
         <is>
-          <t>Brake on +12 V (opto8 i1)</t>
+          <t>Brake on +12 V (opto8 IN1)</t>
         </is>
       </c>
       <c r="S16" s="48" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="AE16" s="54" t="inlineStr">
         <is>
-          <t>splice sp_rl_stop named in SoT; flying lead FL_R12_C1: EWD R12 pin 1 G-W (factory wiring; new wire here)</t>
+          <t>splice sp_rl_stop: node of the wire list (SoT); flying lead FL_R12_C1: EWD R12 pin 1 G-W (factory wiring; new wire here)</t>
         </is>
       </c>
       <c r="AF16" s="54" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="AE17" s="38" t="inlineStr">
         <is>
-          <t>splice sp_rl_tail named in SoT; flying lead FL_L1_C1: EWD L1 pin 1 G (factory wiring; new wire here)</t>
+          <t>splice sp_rl_tail: node of the wire list (SoT); flying lead FL_L1_C1: EWD L1 pin 1 G (factory wiring; new wire here)</t>
         </is>
       </c>
       <c r="AF17" s="38" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="AE18" s="54" t="inlineStr">
         <is>
-          <t>splice sp_rl_tail named in SoT; flying lead FL_R11_C2: EWD R11 pin 2 G (factory wiring; new wire here)</t>
+          <t>splice sp_rl_tail: node of the wire list (SoT); flying lead FL_R11_C2: EWD R11 pin 2 G (factory wiring; new wire here)</t>
         </is>
       </c>
       <c r="AF18" s="54" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="AE19" s="38" t="inlineStr">
         <is>
-          <t>splice sp_rl_tail named in SoT; flying lead FL_R11_C3: EWD R11 pin 3 G (factory wiring; new wire here)</t>
+          <t>splice sp_rl_tail: node of the wire list (SoT); flying lead FL_R11_C3: EWD R11 pin 3 G (factory wiring; new wire here)</t>
         </is>
       </c>
       <c r="AF19" s="38" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="AE20" s="54" t="inlineStr">
         <is>
-          <t>splice sp_rl_tail named in SoT; flying lead FL_R12_C2: EWD R12 pin 2 G (factory wiring; new wire here)</t>
+          <t>splice sp_rl_tail: node of the wire list (SoT); flying lead FL_R12_C2: EWD R12 pin 2 G (factory wiring; new wire here)</t>
         </is>
       </c>
       <c r="AF20" s="54" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="AE21" s="38" t="inlineStr">
         <is>
-          <t>splice sp_rl_tail named in SoT; flying lead FL_R12_C3: EWD R12 pin 3 G (factory wiring; new wire here)</t>
+          <t>splice sp_rl_tail: node of the wire list (SoT); flying lead FL_R12_C3: EWD R12 pin 3 G (factory wiring; new wire here)</t>
         </is>
       </c>
       <c r="AF21" s="38" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="L3" s="38" t="inlineStr">
         <is>
-          <t>named in SoT</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -3790,12 +3790,12 @@
       </c>
       <c r="D4" s="46" t="inlineStr">
         <is>
-          <t>opto8.i1</t>
+          <t>opto8.IN1</t>
         </is>
       </c>
       <c r="E4" s="47" t="inlineStr">
         <is>
-          <t>Brake on +12 V (opto8 i1)</t>
+          <t>Brake on +12 V (opto8 IN1)</t>
         </is>
       </c>
       <c r="F4" s="48" t="n">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="L4" s="54" t="inlineStr">
         <is>
-          <t>named in SoT</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -3880,7 +3880,7 @@
       </c>
       <c r="L5" s="38" t="inlineStr">
         <is>
-          <t>named in SoT</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="L6" s="54" t="inlineStr">
         <is>
-          <t>named in SoT</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>

--- a/docs/harness/wirelist/RearLights-wirelist.xlsx
+++ b/docs/harness/wirelist/RearLights-wirelist.xlsx
@@ -1191,14 +1191,10 @@
       </c>
       <c r="V3" s="34" t="inlineStr">
         <is>
-          <t>White</t>
-        </is>
-      </c>
-      <c r="W3" s="34" t="inlineStr">
-        <is>
           <t>Black</t>
         </is>
       </c>
+      <c r="W3" s="34" t="inlineStr"/>
       <c r="X3" s="34" t="inlineStr">
         <is>
           <t>Yellow</t>
@@ -1324,7 +1320,7 @@
       </c>
       <c r="V4" s="50" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="W4" s="50" t="inlineStr"/>
@@ -1451,14 +1447,10 @@
       </c>
       <c r="V5" s="34" t="inlineStr">
         <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="W5" s="34" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="W5" s="34" t="inlineStr"/>
       <c r="X5" s="34" t="inlineStr">
         <is>
           <t>Blue-White</t>
@@ -1584,14 +1576,10 @@
       </c>
       <c r="V6" s="50" t="inlineStr">
         <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="W6" s="50" t="inlineStr">
-        <is>
-          <t>Black</t>
-        </is>
-      </c>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="W6" s="50" t="inlineStr"/>
       <c r="X6" s="50" t="inlineStr">
         <is>
           <t>Blue-Yellow</t>
@@ -1717,14 +1705,10 @@
       </c>
       <c r="V7" s="34" t="inlineStr">
         <is>
-          <t>White</t>
-        </is>
-      </c>
-      <c r="W7" s="34" t="inlineStr">
-        <is>
           <t>Black</t>
         </is>
       </c>
+      <c r="W7" s="34" t="inlineStr"/>
       <c r="X7" s="34" t="inlineStr">
         <is>
           <t>Yellow</t>
@@ -1848,14 +1832,10 @@
       </c>
       <c r="V8" s="50" t="inlineStr">
         <is>
-          <t>White</t>
-        </is>
-      </c>
-      <c r="W8" s="50" t="inlineStr">
-        <is>
           <t>Black</t>
         </is>
       </c>
+      <c r="W8" s="50" t="inlineStr"/>
       <c r="X8" s="50" t="inlineStr">
         <is>
           <t>Yellow</t>
@@ -1979,14 +1959,10 @@
       </c>
       <c r="V9" s="34" t="inlineStr">
         <is>
-          <t>White</t>
-        </is>
-      </c>
-      <c r="W9" s="34" t="inlineStr">
-        <is>
           <t>Black</t>
         </is>
       </c>
+      <c r="W9" s="34" t="inlineStr"/>
       <c r="X9" s="34" t="inlineStr">
         <is>
           <t>Yellow</t>
@@ -2110,14 +2086,10 @@
       </c>
       <c r="V10" s="50" t="inlineStr">
         <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="W10" s="50" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="W10" s="50" t="inlineStr"/>
       <c r="X10" s="50" t="inlineStr">
         <is>
           <t>Blue-Blue</t>
@@ -2239,14 +2211,10 @@
       </c>
       <c r="V11" s="34" t="inlineStr">
         <is>
-          <t>White</t>
-        </is>
-      </c>
-      <c r="W11" s="34" t="inlineStr">
-        <is>
           <t>Black</t>
         </is>
       </c>
+      <c r="W11" s="34" t="inlineStr"/>
       <c r="X11" s="34" t="inlineStr">
         <is>
           <t>Yellow</t>
@@ -2357,11 +2325,7 @@
           <t>Red</t>
         </is>
       </c>
-      <c r="W12" s="50" t="inlineStr">
-        <is>
-          <t>Black</t>
-        </is>
-      </c>
+      <c r="W12" s="50" t="inlineStr"/>
       <c r="X12" s="50" t="inlineStr">
         <is>
           <t>White</t>
@@ -2488,11 +2452,7 @@
           <t>Red</t>
         </is>
       </c>
-      <c r="W13" s="34" t="inlineStr">
-        <is>
-          <t>Black</t>
-        </is>
-      </c>
+      <c r="W13" s="34" t="inlineStr"/>
       <c r="X13" s="34" t="inlineStr">
         <is>
           <t>White</t>
@@ -2618,14 +2578,10 @@
       </c>
       <c r="V14" s="50" t="inlineStr">
         <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="W14" s="50" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="W14" s="50" t="inlineStr"/>
       <c r="X14" s="50" t="inlineStr">
         <is>
           <t>Blue-Blue</t>
@@ -2749,14 +2705,10 @@
       </c>
       <c r="V15" s="34" t="inlineStr">
         <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="W15" s="34" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="W15" s="34" t="inlineStr"/>
       <c r="X15" s="34" t="inlineStr">
         <is>
           <t>Blue-Blue</t>
@@ -2880,14 +2832,10 @@
       </c>
       <c r="V16" s="50" t="inlineStr">
         <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="W16" s="50" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="W16" s="50" t="inlineStr"/>
       <c r="X16" s="50" t="inlineStr">
         <is>
           <t>Blue-Blue</t>
@@ -3011,7 +2959,7 @@
       </c>
       <c r="V17" s="34" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="W17" s="34" t="inlineStr"/>
@@ -3138,7 +3086,7 @@
       </c>
       <c r="V18" s="50" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="W18" s="50" t="inlineStr"/>
@@ -3265,7 +3213,7 @@
       </c>
       <c r="V19" s="34" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="W19" s="34" t="inlineStr"/>
@@ -3392,7 +3340,7 @@
       </c>
       <c r="V20" s="50" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="W20" s="50" t="inlineStr"/>
@@ -3519,7 +3467,7 @@
       </c>
       <c r="V21" s="34" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="W21" s="34" t="inlineStr"/>
